--- a/tabelle_1_main.xlsx
+++ b/tabelle_1_main.xlsx
@@ -103,7 +103,7 @@
     <t>NaN</t>
   </si>
   <si>
-    <t xml:space="preserve">юугаа ч өхөгөөс буцахгүй дурлах / дуртай байх, ухаан жолоогүй дурлах
+    <t xml:space="preserve">юугаа ч өхөгөөс буцахгүй дурлах / дуртай байх; ухаан жолоогүй дурлах
 </t>
   </si>
   <si>
@@ -174,7 +174,7 @@
     <t>auf; abfahren; abgefahren; fährt; ab; etw. ist abgefahren</t>
   </si>
   <si>
-    <t>15.02.2026_2130: alle Beispiele hinzugefügt, kursiv und grau markiert</t>
+    <t>02.03.2026_1600: alle Beispiele hinzugefügt, kursive Markierung geprüft</t>
   </si>
   <si>
     <t>ph00002</t>
@@ -210,7 +210,7 @@
     <t>Beim Karaoke habe ich mich echt zum Affen gemacht, aber wenigstens hatten alle Spaß.</t>
   </si>
   <si>
-    <t>sich; zum; Affen; machen; habe; mich; gemacht; dich; macht; mach</t>
+    <t>sich; zum; Affen; machen; habe; mich; gemacht; macht; mach dich</t>
   </si>
   <si>
     <t>ph00003</t>
@@ -255,7 +255,7 @@
     <t>Ich habe dich nur auf den Arm genommen. Ich habe das nicht wirklich gemeint.</t>
   </si>
   <si>
-    <t>Spaß machen; jmdn. verarschen; jmdn. veräppeln; auf den Arm; nehmen; genommen; hat; nimmt; veräppelt; verarscht; habe</t>
+    <t>Spaß machen; jmdn. verarschen; jmdn. veräppeln; auf den Arm; nehmen; genommen; hat; nimmt; veräppelt; verarscht;</t>
   </si>
   <si>
     <t>ph00004</t>
@@ -400,7 +400,7 @@
     <t xml:space="preserve">Die neue Mitarbeiterin hat dem Chef bei der Weihnachtsfeier schöne Augen gemacht. </t>
   </si>
   <si>
-    <t>schöne Augen; machen; gemacht</t>
+    <t>schöne Augen; machen; gemacht; hat;</t>
   </si>
   <si>
     <t>ph00008</t>
@@ -418,7 +418,7 @@
     <t>Toleranz</t>
   </si>
   <si>
-    <t>beide Augen zudrücken гэвэл илүү том зүйлийг зүгээр өнгөрөөж бай- гаа гэсэн утга илэрхийлнэ.</t>
+    <t>beide Augen zudrücken гэвэл илүү том зүйлийг зүгээр өнгөрөөж байгаа гэсэн утга илэрхийлнэ.</t>
   </si>
   <si>
     <t>Du hast heute wirklich viel Chaos hinterlassen, aber ich werde diesmal ein Auge zudrücken.</t>
@@ -430,7 +430,7 @@
     <t>Heute war ich schlecht vorbereitet bei der Prüfung, aber ich hoffe, dass mein Lehrer ein Auge zudrückt.</t>
   </si>
   <si>
-    <t>ein Auge; zudrücken; drücke, zu; zudrückt; beide Augen zudrücken</t>
+    <t xml:space="preserve">ein Auge; zudrücken; drücke; zu; zudrückt; beide Augen zudrücken; werde; </t>
   </si>
   <si>
     <t>ph00009</t>
@@ -505,7 +505,7 @@
     <t>Er ist am Ball geblieben und hat schließlich die Prüfung bestanden.</t>
   </si>
   <si>
-    <t>am Ball; bleiben; bleib; geblieben; ist</t>
+    <t>am Ball; bleiben; bleib; ist am Ball geblieben</t>
   </si>
   <si>
     <t>ph00011</t>
@@ -616,7 +616,7 @@
     <t>Was er heute wieder für einen Spruch rausgehauen hat! Er nimmt echt kein Blatt vor den Mund.</t>
   </si>
   <si>
-    <t xml:space="preserve">kein Blatt vor den Mund; nehmen; nimmt; nimmst; </t>
+    <t>kein Blatt vor den Mund; nehmen; nimmt; nimmst; ein Blatt vor den Mund;</t>
   </si>
   <si>
     <t>ph00014</t>
@@ -772,7 +772,7 @@
     <t>Nach dem schweren Niederlage waren alle Spieler am Boden zerstört.</t>
   </si>
   <si>
-    <t>am Boden; zerstört; sein; war; ist; waren; den Boden unter den Füßen verlieren</t>
+    <t>am Boden; zerstört; war; ist am Boden zerstört; waren; den Boden unter den Füßen verlieren</t>
   </si>
   <si>
     <t>ph00018</t>
@@ -811,7 +811,7 @@
     <t>Obwohl wir aus verschiedenen Abteilungen kommen, sitzen wir bei diesem Projekt im gleichen Boot.</t>
   </si>
   <si>
-    <t>im; gleichen; einem; Boot; sitzen; to be in the same boat;</t>
+    <t>im gleichen; in einem; Boot; sitzen; to be in the same boat; sitzen im gleichen Boot</t>
   </si>
   <si>
     <t>ph00019</t>
@@ -1015,7 +1015,30 @@
     <t>Auch wenn es schwierig wird, bleibt sie guter Dinge und kämpft weiter.</t>
   </si>
   <si>
-    <t>guter Dinge; sein; ist; bin; bleibt; aller guten Dinge sind; gute Dinge sein</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">guter Dinge; sein; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>ist sie guter Dinge</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>; bin; bleibt; aller guten Dinge sind; gute Dinge sein</t>
+    </r>
   </si>
   <si>
     <t>ph00025</t>
@@ -1048,7 +1071,30 @@
     <t>Er betrachtet seine Arbeit als sein Ein und Alles.</t>
   </si>
   <si>
-    <t xml:space="preserve">EIn und Alles; sein; ist; bist; </t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">Ein und Alles; war; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>ist</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">; bist; </t>
+    </r>
   </si>
   <si>
     <t>ph00026</t>
@@ -1084,7 +1130,7 @@
     <t>In seinem Vortrag fehlte der rote Faden, sodass das Publikum schnell den Übeblick verlor.</t>
   </si>
   <si>
-    <t xml:space="preserve">roter; Faden; der rote Faden; einen roten; </t>
+    <t xml:space="preserve">roter; Faden; der rote Faden; einen; roten; </t>
   </si>
   <si>
     <t>ph00027</t>
@@ -1279,7 +1325,7 @@
     <t>Als sie die Konzerttickets bekam, sprang er vor Freude an die Decke.</t>
   </si>
   <si>
-    <t>Der Archäologe ist vor Freude an die Decke gesprungen, als er den Dinosaurier- knochen gefunden hat.</t>
+    <t>Der Archäologe ist vor Freude an die Decke gesprungen, als er den Dinosaurierknochen gefunden hat.</t>
   </si>
   <si>
     <t>Ich bin nicht gerade vor Freude an die Decke gesprungen, als meine Tochter sagte, sie wolle Schauspiel studieren.</t>
@@ -1390,7 +1436,7 @@
     <t>Du bezahlst jeden Monat für ein Fitnessstudio, aber du gehst nie hin! Das Geld ist doch zum Fenster hinausgeworfen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Geld; zum Fenster; hinauswerfen; hinausgeworfen; das Geld ist;  </t>
+    <t xml:space="preserve">Geld; zum Fenster; hinauswerfen; hinausgeworfen; das Geld ist; würde  </t>
   </si>
   <si>
     <t>ph00036</t>
@@ -1594,7 +1640,7 @@
     <t>Wenn du jemandem dein Herz ausschüttest, zeigt das, dass du dieser Person wirklich vertraust.</t>
   </si>
   <si>
-    <t>das Herz; ausschütten; hat; ausgeschüttet; ausschüttest</t>
+    <t>Herz; ausschütten; hat; ausgeschüttet; ausschüttest</t>
   </si>
   <si>
     <t>ph00043</t>
@@ -1738,7 +1784,7 @@
     <t>Ich habe mir ein Herz gefasst und meinem Chef endlich meine Meinung gesagt.</t>
   </si>
   <si>
-    <t>sich; ein Herz; fassen; nehmen; nimmt; nahm; habe; gefässt</t>
+    <t>sich; ein Herz; fassen; nehmen; nimmt; nahm; habe; gefasst</t>
   </si>
   <si>
     <t>ph00047</t>
@@ -1774,7 +1820,7 @@
     <t>Wenn ich meine Kinder spielen sehe, geht mir das Herz auf.</t>
   </si>
   <si>
-    <t xml:space="preserve">geht; das Herz; auf; ging; aufgegangen </t>
+    <t xml:space="preserve">geht; das Herz; auf; ging; aufgegangen; ist; Herz </t>
   </si>
   <si>
     <t>ph00048</t>
@@ -1894,7 +1940,7 @@
     <t>Sie trägt ihre Heimat tief im Herzen, auch wenn sie schon lange im Ausland lebt.</t>
   </si>
   <si>
-    <t>im; Herzen; tragen; werde; trage; in; trägt</t>
+    <t>im Herzen; tragen; werde; trage; in meinem Herzen; trägt</t>
   </si>
   <si>
     <t>ph00052</t>
@@ -1960,7 +2006,46 @@
     <t xml:space="preserve">Als er das Jobangebot bekommen hat, war er im siebten Himmel. </t>
   </si>
   <si>
-    <t xml:space="preserve">im siebten Himmel; sein; ist; war;  </t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">im siebten Himmel; sein; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>ist</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>er</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> im siebten Himmel; war;  </t>
+    </r>
   </si>
   <si>
     <t>ph00054</t>
@@ -1981,7 +2066,7 @@
     <t>Denken</t>
   </si>
   <si>
-    <t>“Holzweg” нь тайрсан модыг зөөдөг ойн мухар замыг хэлнэ. Хэрэв явган аялагч энэ замаар андуурч явсан бол зорьсон газраа хүрч чадалгүй буцах шаардлагатай болдог. Эндээс “андуурах” гэсэн нэр томъёо гарч ирсэн байна.</t>
+    <t>Holzweg нь тайрсан модыг зөөдөг ойн мухар замыг хэлнэ. Хэрэв явган аялагч энэ замаар андуурч явсан бол зорьсон газраа хүрч чадалгүй буцах шаардлагатай болдог. Эндээс “андуурах” гэсэн нэр томъёо гарч ирсэн байна.</t>
   </si>
   <si>
     <t>андуурч эндүүрэх</t>
@@ -1999,7 +2084,22 @@
     <t>Er war lange auf dem Holzweg, bevor er die richtige Lösung fand.</t>
   </si>
   <si>
-    <t>auf dem Holzweg; sein; war; bist; ist; "Holzweg";</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>war</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> auf dem Holzweg; sein; bist; ist; auf dem Holzweg; Holzweg; war</t>
+    </r>
   </si>
   <si>
     <t>ph00055</t>
@@ -2023,7 +2123,30 @@
     <t>цаасан малгай өмсгөх; тал засах; jmdm. Honig ums Maul schmieren</t>
   </si>
   <si>
-    <t>Er hat der Chefin wieder Honig um den Mund geschmiert, nur damit sie ihm das neue Projekt gibt.</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">Er </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">hat </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>der Chefin wieder Honig um den Mund geschmiert, nur damit sie ihm das neue Projekt gibt.</t>
+    </r>
   </si>
   <si>
     <t>Der Verkäufer schmierte ihm so lange Honig ums Maul, bis er das Auto schließlich kaufte.</t>
@@ -2032,7 +2155,7 @@
     <t>Sie hat dem Lehrer so lange Komplimente gemacht, bis sie eine bessere Note bekam – das nenne ich Honig ums Maul schmieren.</t>
   </si>
   <si>
-    <t xml:space="preserve">Honig; um den Mund; schmieren; hat; geschmiert; schmierte; ums Maul; </t>
+    <t xml:space="preserve">Honig; um den Mund; schmieren; geschmiert; schmierte; ums Maul; </t>
   </si>
   <si>
     <t>ph00056</t>
@@ -2134,7 +2257,7 @@
     <t>Wir streiten immer wieder, aber jetzt verstehe ich, da liegt der Hund begraben: Er fühlt sich nicht genug wertgeschätzt.</t>
   </si>
   <si>
-    <t>dort; liegt; der Hund begraben; da lag</t>
+    <t>dort; da liegt; der Hund begraben; da lag</t>
   </si>
   <si>
     <t>ph00059</t>
@@ -2167,7 +2290,7 @@
     <t>Er scheint ein richtig harter Hund zu sein, obwohl er doch ganz harmlos aussieht.</t>
   </si>
   <si>
-    <t>harter; Hund; ein</t>
+    <t>harter Hund; ein</t>
   </si>
   <si>
     <t>ph00060</t>
@@ -2227,7 +2350,7 @@
     <t>Kriminalität</t>
   </si>
   <si>
-    <t>“kalt” буюу “хүйтэн” гэдэг нь хүн нас барсны дараа бие нь хөрдөгтэй холбоотой үүссэн үг.</t>
+    <t>kalt буюу “хүйтэн” гэдэг нь хүн нас барсны дараа бие нь хөрдөгтэй холбоотой үүссэн үг.</t>
   </si>
   <si>
     <t>амийг нь хорлох; егүүтгэх, таслах; цааш нь харуулах</t>
@@ -2242,7 +2365,7 @@
     <t>In dem Krimi wollte der Angeklagte eine Zeugin kalt machen.</t>
   </si>
   <si>
-    <t>kalt; machen; macht; “kalt”;</t>
+    <t>kalt; machen; macht er dich kalt;</t>
   </si>
   <si>
     <t>ph00062</t>
@@ -2371,7 +2494,7 @@
     <t>Nun lässt die Regierung die Katze aus dem Sack: Energiepreise werden deutlich teurer als bisher angenommen.</t>
   </si>
   <si>
-    <t>die Katze aus dem Sack; lassen; ist; los; Katze, lässt; die Katze im Sack lassen</t>
+    <t xml:space="preserve">die Katze aus dem Sack lassen; eine Katze aus dem Sack lassen; ist; los, Katze aus dem Sack!; die Katze aus dem Sack; lässt; die Katze im Sack lassen; die Katze im Sack kaufen; lässt; </t>
   </si>
   <si>
     <t>ph00066</t>
@@ -2386,7 +2509,7 @@
     <t>Nervigkeit</t>
   </si>
   <si>
-    <t>нойтон хамуу шиг, залхаах, төвөг болох, jmdm. auf den Geist gehen, jmdm. auf die Nerven gehen, jmdm. auf den Senkel gehen, jmdm. auf die Eier gehen, jmdm. auf  den Wecker gehen, jmdm. auf den Zeiger gehen</t>
+    <t>нойтон хамуу шиг; залхаах; төвөг болох; jmdm. auf den Geist gehen; jmdm. auf die Nerven gehen; jmdm. auf den Senkel gehen; jmdm. auf die Eier gehen; jmdm. auf  den Wecker gehen; jmdm. auf den Zeiger gehen;</t>
   </si>
   <si>
     <t>Kannst du bitte aufhören, mir auf den Keks zu gehen? Ich brauche gerade Ruhe.</t>
@@ -2710,7 +2833,7 @@
     <t>Ein Betriebsausflug hält die Mitarbeiter bei Laune.</t>
   </si>
   <si>
-    <t>bei; Laune; halten; hält; Luna</t>
+    <t>bei Laune; Laune; bei guter Laune; halten; hält; Luna</t>
   </si>
   <si>
     <t>ph00077</t>
@@ -2893,10 +3016,56 @@
     <t>хуучлах, дотроо уудлах; нууцаа задлах, ам алдах</t>
   </si>
   <si>
-    <t>Nach ein paar Drinks fing unser Chef an, aus dem Nähkästchen zu plaudern und hat einige Geheimnisse über die Firma erzählt.</t>
-  </si>
-  <si>
-    <t>Nach dem Essen hat mein Opa von früher erzählt und ein bisschen aus dem Nähkästchen geplaudert, wie er Oma kennengelernt hat.</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>Nach ein paar Drinks fing unser Chef an, aus dem Nähkästchen zu plaudern und</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> hat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> einige Geheimnisse über die Firma erzählt.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">Nach dem Essen hat mein Opa von früher erzählt und ein bisschen aus dem Nähkästchen geplaudert, wie er Oma kennengelernt </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>hat</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
   <si>
     <t>Sie ist eine clevere Journalistin und schafft es immer, dass die Menschen im Interview aus dem Nähkästchen plaudern.</t>
@@ -2905,7 +3074,7 @@
     <t>Manche Leute plaudern gern aus dem Nähkästchen und geben dabei vertrauliche Informationen preis.</t>
   </si>
   <si>
-    <t xml:space="preserve">aus dem Nähkästchen; plaudern; hat; geplaudert; </t>
+    <t xml:space="preserve">aus dem Nähkästchen; plaudern; geplaudert; </t>
   </si>
   <si>
     <t>ph00083</t>
@@ -3175,7 +3344,7 @@
     <t>Unsere Firma verliert ihr bestes Pferd im Stall, wenn Kevin seinen Job kündigt.</t>
   </si>
   <si>
-    <t xml:space="preserve">das beste; Pferd; im Stall; sein; ist; bestes </t>
+    <t xml:space="preserve">das beste; Pferd; im Stall; ist; bestes </t>
   </si>
   <si>
     <t>ph00091</t>
@@ -3241,7 +3410,7 @@
     <t>Er behauptet, dass er mit einem Drachen gekämpft hat – der erzählt mir doch was vom Pferd!</t>
   </si>
   <si>
-    <t xml:space="preserve">einen; vom Pferd; erzählen; erzähl: keinen; erzählt; was; </t>
+    <t xml:space="preserve">einen; vom Pferd; erzählen; erzählt; keinen; was; </t>
   </si>
   <si>
     <t>ph00093</t>
@@ -3310,7 +3479,7 @@
     <t>Mit ihrem Start-up hat sie aufs richtige Pferd gesetzt – jetzt läuft das Geschäft richtig gut.</t>
   </si>
   <si>
-    <t>аufs; falsche; richtige; Pferd; setzen; hat; gesetzt; setzt</t>
+    <t>falsche; richtige; Pferd; setzen; hat; gesetzt; setzt; aufs</t>
   </si>
   <si>
     <t>ph00095</t>
@@ -3331,7 +3500,7 @@
     <t>Verhalten</t>
   </si>
   <si>
-    <t>Дундад зууны Европт язгууртнууд өндөр, сүрлэг морь унадаг байсан нь тэдний нэр төр, эрх мэдлийн бэлгэ тэмдэг байв. Харин энгийн ард морь унах боломж хомс байсан. Иймээс өөрийгөө бус- даас дээгүүр тавих зан авирыг “өндөр морь унахтай” зүйрлэдэг  болжээ.</t>
+    <t>Дундад зууны Европт язгууртнууд өндөр, сүрлэг морь унадаг байсан нь тэдний нэр төр, эрх мэдлийн бэлгэ тэмдэг байв. Харин энгийн ард морь унах боломж хомс байсан. Иймээс өөрийгөө бусдаас дээгүүр тавих зан авирыг “өндөр морь унахтай” зүйрлэдэг  болжээ.</t>
   </si>
   <si>
     <t>хамраа сөхөх</t>
@@ -3364,7 +3533,7 @@
     <t>Unlogisches Vorgehen</t>
   </si>
   <si>
-    <t>“морийг хойноос нь хазаарлах” нь утгагүй бөгөөд боломжгүй зүйл. Тиймээс энэ зүйрлэлээр ажлыг зохих дараа- лалгүй хийж байгааг шүүмжлэхэд хэрэглэдэг.</t>
+    <t>“морийг хойноос нь хазаарлах” нь утгагүй бөгөөд боломжгүй зүйл. Тиймээс энэ зүйрлэлээр ажлыг зохих дараалалгүй хийж байгааг шүүмжлэхэд хэрэглэдэг.</t>
   </si>
   <si>
     <t>Wenn wir zuerst das unwichtigste Problem lösen, zäumen wir das Pferd von hinten auf.</t>
@@ -3376,7 +3545,7 @@
     <t>Du solltest zuerst das Fundament bauen und nicht direkt mit der Einrichtung anfangen, sonst zäumst du das Pferd von hinten auf.</t>
   </si>
   <si>
-    <t xml:space="preserve">das Pferd von hinten; aufzäumen; zäumen; auf; </t>
+    <t xml:space="preserve">das Pferd von hinten; aufzäumen; zäumen; zäumst; auf; </t>
   </si>
   <si>
     <t>ph00097</t>
@@ -3409,7 +3578,7 @@
     <t>Sie blieb viel zu lange in der Beziehung, obwohl alle Anzeichen zeigten, dass sie nicht mehr funktionierte. Sie hat das tote Pferd geritten, anstatt loszulassen und weiterzugehen.</t>
   </si>
   <si>
-    <t>ein totes Pferd; reiten; wird; hat; geritten; riding a dead horse</t>
+    <t>ein totes Pferd; das tote Pferd; reiten; wird; hat; geritten; riding a dead horse</t>
   </si>
   <si>
     <t>ph00098</t>
@@ -3736,7 +3905,7 @@
     <t>Im Streit hat sie ihn so zur Sau gemacht, dass er sprachlos war.</t>
   </si>
   <si>
-    <t>zur Sau; machen; machte; hat; gemacht;</t>
+    <t>zur Sau; machen; machte; hat; zur Sau gemacht;</t>
   </si>
   <si>
     <t>ph00108</t>
@@ -3868,7 +4037,30 @@
     <t>Du hast das ganze Wochenende nur gelesen? Was bist du denn für eine Schlaftablette?</t>
   </si>
   <si>
-    <t>eine; Schlaftablette; sein; ist; Schlaftabletten; sind; dröge sein;</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">eine; Schlaftablette; sein; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>ist;</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve"> Schlaftabletten; sind; dröge sein; bist;</t>
+    </r>
   </si>
   <si>
     <t>ph00112</t>
@@ -3901,7 +4093,7 @@
     <t>Als der Lehrer die Grammatik erklärt hat, stand ich auf dem Schlauch. Ich habe nichts verstanden!</t>
   </si>
   <si>
-    <t>auf dem Schlauch; stehen; stehe; stand</t>
+    <t>auf dem Schlauch; stehe; stand</t>
   </si>
   <si>
     <t>ph00113</t>
@@ -3964,7 +4156,7 @@
     <t>Wieder so eine olle Kamelle, die jeder kennt und niemand mehr hören will!</t>
   </si>
   <si>
-    <t>Scnhee von gestern; olle Kamelle; kalter Kaffee</t>
+    <t>Schnee von gestern; olle Kamelle; kalter Kaffee</t>
   </si>
   <si>
     <t>ph00115</t>
@@ -4000,7 +4192,22 @@
     <t>In einer Partnerschaft ist es wichtig, auch kleine Probleme nicht auf die Schulter zu nehmen.</t>
   </si>
   <si>
-    <t xml:space="preserve">auf die leichte Schulter; nehmen; nimmt; </t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">auf die leichte Schulter; nehmen; nimmt; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>auf die Schulter</t>
+    </r>
   </si>
   <si>
     <t>ph00116</t>
@@ -4070,7 +4277,7 @@
     <t>Für das neue Projekt hat kein Schwein Interesse gezeigt.</t>
   </si>
   <si>
-    <t>kein; armes; Schwein</t>
+    <t>kein; keinem; armes; dummes; Schwein</t>
   </si>
   <si>
     <t>ph00118</t>
@@ -4142,7 +4349,7 @@
     <t>Seine Eltern sind krank und brauchen Hilfe, aber er kümmert sich nicht um sie. Ich finde, er benimmt sich wie ein Schwein.</t>
   </si>
   <si>
-    <t xml:space="preserve">sich; wie ein Schwein; benehmen; benommen; benimmt; hat; </t>
+    <t>hat sich; wie ein Schwein; benehmen; benommen; benimmt sich;</t>
   </si>
   <si>
     <t>ph00120</t>
@@ -4421,7 +4628,7 @@
     <t>Manche Leute verknallen sich schnell und intensiver als andere.</t>
   </si>
   <si>
-    <t xml:space="preserve">sich; in; verknallen; habe; mich; verknallt, war; hat; </t>
+    <t xml:space="preserve">sich; in; verknallen; habe; mich; verknallt; war; hat; </t>
   </si>
   <si>
     <t>ph00129</t>
@@ -4457,7 +4664,7 @@
     <t>Bei dieser Kälte noch Eis essen? Hast du einen Vogel?</t>
   </si>
   <si>
-    <t>einen Vogel; haben, hat; hast; zeigen; zeigte; jmdm. einen Vogel zeigen</t>
+    <t>einen Vogel; den Vogel; hat; hast; zeigen; zeigte; jmdm. einen Vogel zeigen</t>
   </si>
   <si>
     <t>ph00130</t>
@@ -4490,7 +4697,7 @@
     <t>Du hast doch einen an der Waffel, so etwas macht man nicht.</t>
   </si>
   <si>
-    <t>einen an der; Waffel; haben; hast; waffeln; waffle</t>
+    <t>einen an der; Waffel; haben; hast; waffeln; waffle; schwafeln;</t>
   </si>
   <si>
     <t>ph00131</t>
@@ -4583,7 +4790,30 @@
     <t>Der Lehrer hat beim Abschied fast geweint – er ist eben nah am Wasser gebaut.</t>
   </si>
   <si>
-    <t xml:space="preserve">nah am Wasser; gebaut; sein; bin; war; ist; Heulsuse; </t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">nah am Wasser; gebaut; sein; bin; war; </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FFFF0000"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t>ist</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+        <sz val="9.0"/>
+      </rPr>
+      <t xml:space="preserve">; Heulsuse; </t>
+    </r>
   </si>
   <si>
     <t>ph00134</t>
@@ -4742,10 +4972,10 @@
     <t>Sie hat sich den ganzen Tag einen Wolf gesucht, um die verlorenen Dokumente zu finden.</t>
   </si>
   <si>
-    <t>Ich habe mir einen Wolf gesucht, konnte meine Schlüssel aber nicht finden..</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sich; einen Wolf; suchen; habe; mir; gesucht; hat; </t>
+    <t>Ich habe mir einen Wolf gesucht, konnte meine Schlüssel aber nicht finden.</t>
+  </si>
+  <si>
+    <t>sich; einen Wolf gesucht; suchen; hab; mir; hat; habe mir einen Wolf gesucht;</t>
   </si>
   <si>
     <t>ph00139</t>
@@ -4926,8 +5156,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -6199,7 +6429,7 @@
       <c r="AE15" s="2"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="1" t="s">
         <v>196</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -6796,7 +7026,7 @@
       <c r="AE24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="7" t="s">
         <v>303</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -6863,7 +7093,7 @@
       <c r="AE25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="7" t="s">
         <v>316</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -7198,7 +7428,7 @@
       <c r="AE30" s="2"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="1" t="s">
         <v>375</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -7396,7 +7626,7 @@
       <c r="A34" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -7789,7 +8019,7 @@
       <c r="AE39" s="2"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="1" t="s">
         <v>477</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -8379,7 +8609,7 @@
       <c r="A49" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="1" t="s">
         <v>579</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -8638,7 +8868,7 @@
       <c r="AE52" s="2"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="7" t="s">
         <v>620</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -8703,7 +8933,7 @@
       <c r="AE53" s="2"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="7" t="s">
         <v>631</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -8770,7 +9000,7 @@
       <c r="AE54" s="2"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="7" t="s">
         <v>644</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -9359,7 +9589,7 @@
       <c r="AE63" s="2"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="1" t="s">
         <v>745</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -9754,7 +9984,7 @@
       <c r="A70" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="1" t="s">
         <v>810</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -9821,7 +10051,7 @@
       <c r="A71" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="B71" s="7" t="s">
+      <c r="B71" s="1" t="s">
         <v>820</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -9885,7 +10115,7 @@
       <c r="AE71" s="2"/>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="s">
+      <c r="A72" s="1" t="s">
         <v>831</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -10414,7 +10644,7 @@
       <c r="A80" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B80" s="1" t="s">
         <v>914</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -10547,7 +10777,7 @@
       <c r="AE81" s="2"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="7" t="s">
         <v>936</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -10681,7 +10911,7 @@
       <c r="AE83" s="2"/>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="s">
+      <c r="A84" s="1" t="s">
         <v>958</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -11144,7 +11374,7 @@
       <c r="AE90" s="2"/>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="s">
+      <c r="A91" s="1" t="s">
         <v>1036</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -11276,7 +11506,7 @@
       <c r="AE92" s="2"/>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="s">
+      <c r="A93" s="1" t="s">
         <v>1058</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -12263,7 +12493,7 @@
       <c r="AE107" s="2"/>
     </row>
     <row r="108">
-      <c r="A108" s="7" t="s">
+      <c r="A108" s="1" t="s">
         <v>1223</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -12396,7 +12626,7 @@
       <c r="A110" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="1" t="s">
         <v>1244</v>
       </c>
       <c r="C110" s="1" t="s">
@@ -12462,7 +12692,7 @@
       <c r="AE110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="7" t="s">
         <v>1255</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -12730,7 +12960,7 @@
       <c r="AE114" s="2"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="7" t="s">
         <v>1299</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -13462,7 +13692,7 @@
       <c r="A126" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="1" t="s">
         <v>1420</v>
       </c>
       <c r="C126" s="1" t="s">
@@ -13922,7 +14152,7 @@
       <c r="AE132" s="2"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="7" t="s">
         <v>1493</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -14117,7 +14347,7 @@
       <c r="AE135" s="2"/>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="s">
+      <c r="A136" s="1" t="s">
         <v>1523</v>
       </c>
       <c r="B136" s="1" t="s">

--- a/tabelle_1_main.xlsx
+++ b/tabelle_1_main.xlsx
@@ -174,7 +174,7 @@
     <t>auf; abfahren; abgefahren; fährt; ab; etw. ist abgefahren</t>
   </si>
   <si>
-    <t>02.03.2026_1600: alle Beispiele hinzugefügt, kursive Markierung geprüft</t>
+    <t>02.03.2026_1645: alle Beispiele hinzugefügt, kursive Markierung geprüft; aktuelle Tabelle Checkfunktion</t>
   </si>
   <si>
     <t>ph00002</t>

--- a/tabelle_1_main.xlsx
+++ b/tabelle_1_main.xlsx
@@ -76,7 +76,7 @@
     <t>ph00001</t>
   </si>
   <si>
-    <t>auf jmdn./ etw. abfahren</t>
+    <t>auf jmdn./ etw. abfahren test</t>
   </si>
   <si>
     <t>хэн нэгэнд буюу ямар нэгэн зүйлд хэт их татагдах, дурлах, бишрэх</t>
@@ -174,7 +174,7 @@
     <t>auf; abfahren; abgefahren; fährt; ab; etw. ist abgefahren</t>
   </si>
   <si>
-    <t>02.03.2026_1645: alle Beispiele hinzugefügt, kursive Markierung geprüft; aktuelle Tabelle Checkfunktion</t>
+    <t>02.03.2026_1645: alle Beispiele hinzugefügt, kursive Markierung geprüft; aktuelle Tabelle Checkfunktion test test</t>
   </si>
   <si>
     <t>ph00002</t>

--- a/tabelle_1_main.xlsx
+++ b/tabelle_1_main.xlsx
@@ -76,7 +76,7 @@
     <t>ph00001</t>
   </si>
   <si>
-    <t>auf jmdn./ etw. abfahren test</t>
+    <t>auf jmdn./ etw. abfahren</t>
   </si>
   <si>
     <t>хэн нэгэнд буюу ямар нэгэн зүйлд хэт их татагдах, дурлах, бишрэх</t>
@@ -174,7 +174,7 @@
     <t>auf; abfahren; abgefahren; fährt; ab; etw. ist abgefahren</t>
   </si>
   <si>
-    <t>02.03.2026_1645: alle Beispiele hinzugefügt, kursive Markierung geprüft; aktuelle Tabelle Checkfunktion test test</t>
+    <t>02.03.2026_1700: alle Beispiele hinzugefügt, kursive Markierung geprüft; aktuelle Tabelle Checkfunktion</t>
   </si>
   <si>
     <t>ph00002</t>
